--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487818_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487818_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. OBAJO BELTRAN</t>
+          <t>B. AREVALO SAENZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8147</v>
+        <v>4.3256</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8745</v>
+        <v>5.9002</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0598</v>
+        <v>-1.5746</v>
       </c>
       <c r="G2" t="n">
-        <v>1.4265</v>
+        <v>1.8271</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5629</v>
+        <v>0.2922</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.1365</v>
+        <v>1.5349</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6636</v>
+        <v>4.3011</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3387</v>
+        <v>1.1661</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6752</v>
+        <v>3.1351</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.2371</v>
+        <v>-2.474</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7758</v>
+        <v>-0.8738</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4613</v>
+        <v>-1.6002</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.6649</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8045</v>
+        <v>-0.1041</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4378</v>
+        <v>0.4315</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3667</v>
+        <v>-0.5356</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5838</v>
+        <v>0.9376</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8137</v>
+        <v>1.1675</v>
       </c>
       <c r="X2" t="n">
         <v>-0.23</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. AREVALO SAENZ</t>
+          <t>L. OBAJO BELTRAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6631</v>
+        <v>2.8737</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0615</v>
+        <v>2.9335</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3985</v>
+        <v>-0.0598</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8271</v>
+        <v>1.4265</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2922</v>
+        <v>2.5629</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5349</v>
+        <v>-1.1365</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3011</v>
+        <v>2.6636</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1661</v>
+        <v>3.3387</v>
       </c>
       <c r="L3" t="n">
-        <v>3.1351</v>
+        <v>-0.6752</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.474</v>
+        <v>-1.2371</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8738</v>
+        <v>-0.7758</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6002</v>
+        <v>-0.4613</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6649</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7665999999999999</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4071</v>
+        <v>0.4968</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3594</v>
+        <v>0.3667</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9376</v>
+        <v>0.5838</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1675</v>
+        <v>0.8137</v>
       </c>
       <c r="X3" t="n">
         <v>-0.23</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4955</v>
+        <v>0.5249</v>
       </c>
       <c r="E4" t="n">
         <v>1.0762</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5807</v>
+        <v>-0.5514</v>
       </c>
       <c r="G4" t="n">
         <v>-1.0426</v>
@@ -766,13 +766,13 @@
         <v>0.6244</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2538</v>
+        <v>-0.2244</v>
       </c>
       <c r="T4" t="n">
         <v>-0.1305</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1233</v>
+        <v>-0.0939</v>
       </c>
       <c r="V4" t="n">
         <v>1.1675</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ MONTON</t>
+          <t>A. PLITZUWEIT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0512</v>
+        <v>0.4972</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2034</v>
+        <v>1.6667</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2546</v>
+        <v>-1.1694</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0453</v>
+        <v>-2.6641</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2943</v>
+        <v>0.431</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.249</v>
+        <v>-3.0951</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0576</v>
+        <v>-1.3045</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0576</v>
+        <v>0.9742</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-2.2787</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0123</v>
+        <v>-1.3596</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2367</v>
+        <v>-0.5432</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.249</v>
+        <v>-0.8164</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2081</v>
+        <v>1.8731</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2023</v>
+        <v>-0.0062</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.261</v>
+        <v>0.5091</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0587</v>
+        <v>-0.5153</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.3351</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.5026</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. PLITZUWEIT</t>
+          <t>A. RODRIGUEZ MONTON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0303</v>
+        <v>0.1392</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2566</v>
+        <v>-0.2034</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2869</v>
+        <v>0.3427</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.6641</v>
+        <v>0.0453</v>
       </c>
       <c r="H6" t="n">
-        <v>0.431</v>
+        <v>0.2943</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.0951</v>
+        <v>-0.249</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.3045</v>
+        <v>0.0576</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9742</v>
+        <v>0.0576</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.2787</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3596</v>
+        <v>-0.0123</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5432</v>
+        <v>0.2367</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8164</v>
+        <v>-0.249</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8731</v>
+        <v>0.2081</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5337</v>
+        <v>-0.1142</v>
       </c>
       <c r="T6" t="n">
-        <v>0.09909999999999999</v>
+        <v>-0.261</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6328</v>
+        <v>0.1468</v>
       </c>
       <c r="V6" t="n">
-        <v>2.3351</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>3.5026</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.577</v>
+        <v>-0.0054</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.366</v>
+        <v>0.235</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.211</v>
+        <v>-0.2404</v>
       </c>
       <c r="G7" t="n">
         <v>-1.228</v>
@@ -1000,13 +1000,13 @@
         <v>1.2487</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7216</v>
+        <v>-0.1499</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.09329999999999999</v>
+        <v>0.5077</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6282</v>
+        <v>-0.6576</v>
       </c>
       <c r="V7" t="n">
         <v>0.1238</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6248</v>
+        <v>-1.7841</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1977</v>
+        <v>0.1558</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8225</v>
+        <v>-1.9399</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8231000000000001</v>
@@ -1078,13 +1078,13 @@
         <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5708</v>
+        <v>0.4115</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4253</v>
+        <v>0.3834</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1455</v>
+        <v>0.0281</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1238</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. SANTOS SPENCER</t>
+          <t>W. NIANG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8683</v>
+        <v>-2.2209</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5751</v>
+        <v>-2.9297</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.4434</v>
+        <v>0.7088</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5814</v>
+        <v>-2.1543</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3755</v>
+        <v>-0.0936</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.206</v>
+        <v>-2.0607</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3581</v>
+        <v>-1.6234</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7883</v>
+        <v>-0.273</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5699</v>
+        <v>-1.3504</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.9396</v>
+        <v>-0.5308</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1637</v>
+        <v>0.1794</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.7758</v>
+        <v>-0.7103</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0451</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6707</v>
+        <v>-0.2657</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6256</v>
+        <v>-0.4253</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1238</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6275</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7513</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W. NIANG</t>
+          <t>P. SANTOS SPENCER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6077</v>
+        <v>-2.6347</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3164</v>
+        <v>1.9555</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7088</v>
+        <v>-4.5902</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1543</v>
+        <v>-2.5814</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0936</v>
+        <v>-0.3755</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.0607</v>
+        <v>-2.206</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6234</v>
+        <v>1.3581</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.273</v>
+        <v>0.7883</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3504</v>
+        <v>0.5699</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5308</v>
+        <v>-3.9396</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1794</v>
+        <v>-1.1637</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7103</v>
+        <v>-2.7758</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6244</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0778</v>
+        <v>0.2787</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6524</v>
+        <v>1.0511</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4253</v>
+        <v>-0.7724</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.1238</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.6275</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.468</v>
+        <v>-2.7854</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5075</v>
+        <v>-1.9717</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9605</v>
+        <v>-0.8137</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1091</v>
@@ -1312,13 +1312,13 @@
         <v>1.4568</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7751</v>
+        <v>-0.0925</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7705</v>
+        <v>-0.2347</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0045</v>
+        <v>0.1423</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8142</v>
+        <v>-3.9171</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9938</v>
+        <v>-2.1847</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8204</v>
+        <v>-1.7323</v>
       </c>
       <c r="G12" t="n">
         <v>-6.6578</v>
@@ -1390,13 +1390,13 @@
         <v>1.0406</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3816</v>
+        <v>0.2787</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.3367</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1461</v>
+        <v>-0.058</v>
       </c>
       <c r="V12" t="n">
         <v>3.5026</v>
@@ -1423,28 +1423,28 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.965800000000001</v>
+        <v>-4.987000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>5.654500000000001</v>
+        <v>6.633400000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.6203</v>
+        <v>-11.6202</v>
       </c>
       <c r="G13" t="n">
         <v>-16.9615</v>
       </c>
       <c r="H13" t="n">
-        <v>2.122399999999999</v>
+        <v>2.1224</v>
       </c>
       <c r="I13" t="n">
         <v>-19.0841</v>
       </c>
       <c r="J13" t="n">
-        <v>1.389600000000001</v>
+        <v>1.389600000000002</v>
       </c>
       <c r="K13" t="n">
-        <v>6.7782</v>
+        <v>6.778199999999999</v>
       </c>
       <c r="L13" t="n">
         <v>-5.3885</v>
@@ -1459,7 +1459,7 @@
         <v>-13.6955</v>
       </c>
       <c r="P13" t="n">
-        <v>3.1218</v>
+        <v>3.121800000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-10.406</v>
@@ -1468,13 +1468,13 @@
         <v>13.5277</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5289000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8458</v>
+        <v>2.8244</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.3743</v>
+        <v>-2.3742</v>
       </c>
       <c r="V13" t="n">
         <v>8.402799999999999</v>
@@ -1483,7 +1483,7 @@
         <v>12.8251</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.4225</v>
+        <v>-4.422499999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0163</v>
+        <v>6.6718</v>
       </c>
       <c r="E14" t="n">
-        <v>7.953</v>
+        <v>7.5244</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9367</v>
+        <v>-0.8525</v>
       </c>
       <c r="G14" t="n">
         <v>7.5754</v>
@@ -1546,13 +1546,13 @@
         <v>1.4568</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9891</v>
+        <v>0.6446</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0621</v>
+        <v>0.6334</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.073</v>
+        <v>0.0111</v>
       </c>
       <c r="V14" t="n">
         <v>0.1168</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2134</v>
+        <v>1.5554</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0037</v>
+        <v>2.1108</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7903</v>
+        <v>-0.5554</v>
       </c>
       <c r="G15" t="n">
         <v>-0.279</v>
@@ -1624,13 +1624,13 @@
         <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9492</v>
+        <v>-0.6072</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4567</v>
+        <v>-0.3495</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4925</v>
+        <v>-0.2577</v>
       </c>
       <c r="V15" t="n">
         <v>1.401</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.92</v>
+        <v>1.1828</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.8573</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3842</v>
+        <v>0.3255</v>
       </c>
       <c r="G16" t="n">
         <v>0.8005</v>
@@ -1702,13 +1702,13 @@
         <v>1.0406</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3373</v>
+        <v>-0.0745</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5219</v>
+        <v>-0.2005</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1847</v>
+        <v>0.1259</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5838</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. DJERY</t>
+          <t>A. CALVO TORRES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7532</v>
+        <v>1.1602</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3139</v>
+        <v>2.817</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5607</v>
+        <v>-1.6568</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9899</v>
+        <v>5.0162</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4201</v>
+        <v>0.8165</v>
       </c>
       <c r="I17" t="n">
-        <v>1.41</v>
+        <v>4.1997</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4882</v>
+        <v>5.0368</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5476</v>
+        <v>1.4495</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9405</v>
+        <v>3.5873</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4982</v>
+        <v>-0.0206</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9677</v>
+        <v>-0.6329</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4695</v>
+        <v>0.6123</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8325</v>
+        <v>-2.0812</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8731</v>
+        <v>1.0406</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7953</v>
+        <v>0.4435</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8663</v>
+        <v>0.3182</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.1253</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.8645</v>
+        <v>-2.2183</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.8645</v>
+        <v>-2.8021</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. ELSO GONZALEZ</t>
+          <t>J. DJERY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1624</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1.0996</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1624</v>
+        <v>-0.4257</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1429</v>
+        <v>0.9899</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0.4201</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1429</v>
+        <v>1.41</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1.4882</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.5476</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.9405</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1429</v>
+        <v>-0.4982</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.9677</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1429</v>
+        <v>0.4695</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.8325</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0196</v>
+        <v>0.716</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.652</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0196</v>
+        <v>0.064</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.8645</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.8645</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1304</v>
+        <v>0.5292</v>
       </c>
       <c r="E19" t="n">
         <v>0.0106</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.141</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>2.8928</v>
@@ -1936,13 +1936,13 @@
         <v>1.6649</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1618</v>
+        <v>0.4978</v>
       </c>
       <c r="T19" t="n">
         <v>0.6054</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7671</v>
+        <v>-0.1076</v>
       </c>
       <c r="V19" t="n">
         <v>-1.4046</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CALVO TORRES</t>
+          <t>A. ALFAMA AMADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.132</v>
+        <v>0.2701</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0669</v>
+        <v>-1.9802</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1989</v>
+        <v>2.2503</v>
       </c>
       <c r="G20" t="n">
-        <v>5.0162</v>
+        <v>1.2797</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8165</v>
+        <v>-0.2111</v>
       </c>
       <c r="I20" t="n">
-        <v>4.1997</v>
+        <v>1.4908</v>
       </c>
       <c r="J20" t="n">
-        <v>5.0368</v>
+        <v>0.1696</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4495</v>
+        <v>-0.1048</v>
       </c>
       <c r="L20" t="n">
-        <v>3.5873</v>
+        <v>0.2743</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0206</v>
+        <v>1.1102</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6329</v>
+        <v>-0.1063</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6123</v>
+        <v>1.2165</v>
       </c>
       <c r="P20" t="n">
+        <v>-1.2487</v>
+      </c>
+      <c r="Q20" t="n">
         <v>-2.0812</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-3.1218</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8487</v>
+        <v>0.4691</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4319</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4168</v>
+        <v>0.5376</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.2183</v>
+        <v>-0.23</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.8021</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ALFAMA AMADO</t>
+          <t>P. ELSO GONZALEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3013</v>
+        <v>0.1918</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9802</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6788</v>
+        <v>0.1918</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2797</v>
+        <v>0.1429</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2111</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4908</v>
+        <v>0.1429</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1696</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1048</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2743</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1102</v>
+        <v>0.1429</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1063</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.2165</v>
+        <v>0.1429</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8325</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1024</v>
+        <v>0.0489</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0339</v>
+        <v>0.0489</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.536</v>
+        <v>-3.4122</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2835</v>
+        <v>-0.8193</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.2524</v>
+        <v>-2.5929</v>
       </c>
       <c r="G22" t="n">
         <v>-1.457</v>
@@ -2170,13 +2170,13 @@
         <v>1.4568</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1241</v>
+        <v>1.2479</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3197</v>
+        <v>0.784</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1957</v>
+        <v>0.4639</v>
       </c>
       <c r="V22" t="n">
         <v>-3.6193</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5.9656</v>
+        <v>8.822999999999999</v>
       </c>
       <c r="E23" t="n">
         <v>11.6202</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.6546</v>
+        <v>-2.7971</v>
       </c>
       <c r="G23" t="n">
         <v>16.9614</v>
@@ -2248,13 +2248,13 @@
         <v>10.4059</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5286999999999999</v>
+        <v>3.3861</v>
       </c>
       <c r="T23" t="n">
         <v>2.3745</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.8457</v>
+        <v>1.0114</v>
       </c>
       <c r="V23" t="n">
         <v>-8.402699999999999</v>
